--- a/output/stock_quant_scores/KMI_cash_flow_df.xlsx
+++ b/output/stock_quant_scores/KMI_cash_flow_df.xlsx
@@ -1532,7 +1532,9 @@
       <c r="A6" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>4427000000</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
